--- a/output/pdf_financials_xlsx/COLL.P.xlsx
+++ b/output/pdf_financials_xlsx/COLL.P.xlsx
@@ -4412,25 +4412,25 @@
         <v>0</v>
       </c>
       <c r="E92" s="3" t="n">
-        <v>0</v>
+        <v>0.030258</v>
       </c>
       <c r="F92" s="3" t="n">
-        <v>0</v>
+        <v>0.030258</v>
       </c>
       <c r="G92" s="3" t="n">
-        <v>0</v>
+        <v>0.030258</v>
       </c>
       <c r="H92" s="3" t="n">
-        <v>0</v>
+        <v>0.030258</v>
       </c>
       <c r="I92" s="3" t="n">
-        <v>0</v>
+        <v>0.030258</v>
       </c>
       <c r="J92" s="3" t="n">
-        <v>0</v>
+        <v>0.030258</v>
       </c>
       <c r="K92" s="3" t="n">
-        <v>0</v>
+        <v>0.030258</v>
       </c>
     </row>
     <row r="93">
@@ -6706,7 +6706,11 @@
           <t>Reserves (Note 4) 30,258</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr"/>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E8" t="inlineStr">
         <is>
           <t>-</t>
@@ -8188,7 +8192,11 @@
           <t>Reserves (Note 5)</t>
         </is>
       </c>
-      <c r="D30" t="inlineStr"/>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E30" t="inlineStr">
         <is>
           <t>-</t>
@@ -8654,7 +8662,11 @@
           <t>Reserves (Note 4)</t>
         </is>
       </c>
-      <c r="D37" t="inlineStr"/>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E37" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/COLL.P.xlsx
+++ b/output/pdf_financials_xlsx/COLL.P.xlsx
@@ -932,10 +932,10 @@
         <v>0</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>0</v>
+        <v>0.006185</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>0</v>
+        <v>0.010821</v>
       </c>
       <c r="G12" s="1" t="inlineStr">
         <is>
@@ -1695,10 +1695,10 @@
         <v>-0.023074</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>-0.035919</v>
+        <v>-0.042104</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>-0.025273</v>
+        <v>-0.036094</v>
       </c>
       <c r="G27" s="1" t="inlineStr">
         <is>
@@ -1795,10 +1795,10 @@
         <v>-0.023074</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>-0.035919</v>
+        <v>-0.042104</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>-0.025273</v>
+        <v>-0.036094</v>
       </c>
       <c r="G29" s="1" t="inlineStr">
         <is>
@@ -2010,10 +2010,10 @@
         </is>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>0.13996</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>0.38378</v>
       </c>
       <c r="E34" s="3" t="n">
         <v>0.710973</v>
@@ -2088,10 +2088,10 @@
         </is>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>0.13996</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>0.38378</v>
       </c>
       <c r="E36" s="3" t="n">
         <v>0.710973</v>
@@ -2559,7 +2559,7 @@
         <v>0</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>0.38878</v>
+        <v>0.005</v>
       </c>
       <c r="E48" s="3" t="n">
         <v>0.0052</v>
@@ -8860,7 +8860,7 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
@@ -14682,7 +14682,7 @@
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E128" t="inlineStr">
